--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Steffano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergioruiz\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15013D12-0D27-41BB-A4FE-E5AD119E48A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44224D1F-1513-40BC-8FE7-F02BEEC9A24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="1525">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -4575,6 +4575,42 @@
   </si>
   <si>
     <t>GRUPO DE ARTÍCULOS</t>
+  </si>
+  <si>
+    <t>M9020125</t>
+  </si>
+  <si>
+    <t>MANJAR CASERO - DULZURA</t>
+  </si>
+  <si>
+    <t>M6020183</t>
+  </si>
+  <si>
+    <t>GALLETA EN FORMA DE SOMBRERO POMO</t>
+  </si>
+  <si>
+    <t>M6020271</t>
+  </si>
+  <si>
+    <t>CASA DE JENGIBRE 2026</t>
+  </si>
+  <si>
+    <t>M6020187</t>
+  </si>
+  <si>
+    <t>GALLETA FORMA FANTASMA POMO</t>
+  </si>
+  <si>
+    <t>M6020081</t>
+  </si>
+  <si>
+    <t>GALLETA EN FORMA DE FANTASMA PETIT</t>
+  </si>
+  <si>
+    <t>M6020270</t>
+  </si>
+  <si>
+    <t>GALLETA FORMA DE CALABAZA STBX</t>
   </si>
 </sst>
 </file>
@@ -4647,7 +4683,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -4952,16 +4988,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D749"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D756"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="103.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4975,7 +5011,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1385</v>
       </c>
@@ -4989,7 +5025,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -5003,7 +5039,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>168</v>
       </c>
@@ -5017,7 +5053,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -5031,7 +5067,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>172</v>
       </c>
@@ -5045,7 +5081,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>174</v>
       </c>
@@ -5059,7 +5095,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>176</v>
       </c>
@@ -5073,7 +5109,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>178</v>
       </c>
@@ -5087,7 +5123,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1387</v>
       </c>
@@ -5101,7 +5137,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>180</v>
       </c>
@@ -5115,7 +5151,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>182</v>
       </c>
@@ -5129,7 +5165,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>184</v>
       </c>
@@ -5143,7 +5179,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>186</v>
       </c>
@@ -5157,7 +5193,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>188</v>
       </c>
@@ -5171,7 +5207,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>190</v>
       </c>
@@ -5185,7 +5221,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>192</v>
       </c>
@@ -5199,7 +5235,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>194</v>
       </c>
@@ -5213,7 +5249,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>196</v>
       </c>
@@ -5227,7 +5263,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>198</v>
       </c>
@@ -5241,7 +5277,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>200</v>
       </c>
@@ -5255,7 +5291,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>202</v>
       </c>
@@ -5269,7 +5305,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>204</v>
       </c>
@@ -5283,7 +5319,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>206</v>
       </c>
@@ -5297,7 +5333,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>208</v>
       </c>
@@ -5311,7 +5347,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>210</v>
       </c>
@@ -5325,7 +5361,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>212</v>
       </c>
@@ -5339,7 +5375,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>214</v>
       </c>
@@ -5353,7 +5389,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>216</v>
       </c>
@@ -5367,7 +5403,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>218</v>
       </c>
@@ -5381,7 +5417,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>220</v>
       </c>
@@ -5395,7 +5431,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>222</v>
       </c>
@@ -5409,7 +5445,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>224</v>
       </c>
@@ -5423,7 +5459,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>226</v>
       </c>
@@ -5437,7 +5473,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>228</v>
       </c>
@@ -5451,7 +5487,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>230</v>
       </c>
@@ -5465,7 +5501,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>232</v>
       </c>
@@ -5479,7 +5515,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>234</v>
       </c>
@@ -5493,7 +5529,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>236</v>
       </c>
@@ -5507,7 +5543,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>238</v>
       </c>
@@ -5521,7 +5557,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>240</v>
       </c>
@@ -5535,7 +5571,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>242</v>
       </c>
@@ -5549,7 +5585,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1389</v>
       </c>
@@ -5563,7 +5599,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1391</v>
       </c>
@@ -5577,7 +5613,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1393</v>
       </c>
@@ -5591,7 +5627,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1395</v>
       </c>
@@ -5605,7 +5641,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>244</v>
       </c>
@@ -5619,7 +5655,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>129</v>
       </c>
@@ -5633,7 +5669,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>246</v>
       </c>
@@ -5647,7 +5683,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>248</v>
       </c>
@@ -5661,7 +5697,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>250</v>
       </c>
@@ -5675,7 +5711,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>252</v>
       </c>
@@ -5689,7 +5725,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>254</v>
       </c>
@@ -5703,7 +5739,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1398</v>
       </c>
@@ -5717,7 +5753,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -5731,7 +5767,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>255</v>
       </c>
@@ -5745,7 +5781,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>257</v>
       </c>
@@ -5759,7 +5795,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>259</v>
       </c>
@@ -5773,7 +5809,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1400</v>
       </c>
@@ -5787,7 +5823,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1402</v>
       </c>
@@ -5801,7 +5837,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>261</v>
       </c>
@@ -5815,7 +5851,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>263</v>
       </c>
@@ -5829,7 +5865,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>265</v>
       </c>
@@ -5843,7 +5879,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>267</v>
       </c>
@@ -5857,7 +5893,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>269</v>
       </c>
@@ -5871,7 +5907,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>271</v>
       </c>
@@ -5885,7 +5921,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>273</v>
       </c>
@@ -5899,7 +5935,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>275</v>
       </c>
@@ -5913,7 +5949,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>277</v>
       </c>
@@ -5927,7 +5963,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>279</v>
       </c>
@@ -5941,7 +5977,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>280</v>
       </c>
@@ -5955,7 +5991,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>282</v>
       </c>
@@ -5969,7 +6005,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>284</v>
       </c>
@@ -5983,7 +6019,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>286</v>
       </c>
@@ -5997,7 +6033,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>288</v>
       </c>
@@ -6011,7 +6047,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>290</v>
       </c>
@@ -6025,7 +6061,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>292</v>
       </c>
@@ -6039,7 +6075,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>294</v>
       </c>
@@ -6053,7 +6089,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>296</v>
       </c>
@@ -6067,7 +6103,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>298</v>
       </c>
@@ -6081,7 +6117,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>300</v>
       </c>
@@ -6095,7 +6131,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>302</v>
       </c>
@@ -6109,7 +6145,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>304</v>
       </c>
@@ -6123,7 +6159,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>306</v>
       </c>
@@ -6137,7 +6173,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>308</v>
       </c>
@@ -6151,7 +6187,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>310</v>
       </c>
@@ -6165,7 +6201,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>312</v>
       </c>
@@ -6179,7 +6215,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>314</v>
       </c>
@@ -6193,7 +6229,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>315</v>
       </c>
@@ -6207,7 +6243,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>317</v>
       </c>
@@ -6221,7 +6257,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>319</v>
       </c>
@@ -6235,7 +6271,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>321</v>
       </c>
@@ -6249,7 +6285,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>322</v>
       </c>
@@ -6263,7 +6299,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>324</v>
       </c>
@@ -6277,7 +6313,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>326</v>
       </c>
@@ -6291,7 +6327,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>328</v>
       </c>
@@ -6305,7 +6341,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>330</v>
       </c>
@@ -6319,7 +6355,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>332</v>
       </c>
@@ -6333,7 +6369,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>333</v>
       </c>
@@ -6347,7 +6383,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>335</v>
       </c>
@@ -6361,7 +6397,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>337</v>
       </c>
@@ -6375,7 +6411,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>339</v>
       </c>
@@ -6389,7 +6425,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>341</v>
       </c>
@@ -6403,7 +6439,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>343</v>
       </c>
@@ -6417,7 +6453,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>345</v>
       </c>
@@ -6431,7 +6467,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>347</v>
       </c>
@@ -6445,7 +6481,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>349</v>
       </c>
@@ -6459,7 +6495,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>351</v>
       </c>
@@ -6473,7 +6509,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>353</v>
       </c>
@@ -6487,7 +6523,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>355</v>
       </c>
@@ -6501,7 +6537,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>357</v>
       </c>
@@ -6515,7 +6551,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>359</v>
       </c>
@@ -6529,7 +6565,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>361</v>
       </c>
@@ -6543,7 +6579,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>363</v>
       </c>
@@ -6557,7 +6593,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>365</v>
       </c>
@@ -6571,7 +6607,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>367</v>
       </c>
@@ -6585,7 +6621,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>369</v>
       </c>
@@ -6599,7 +6635,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>371</v>
       </c>
@@ -6613,7 +6649,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>372</v>
       </c>
@@ -6627,7 +6663,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>374</v>
       </c>
@@ -6641,7 +6677,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>376</v>
       </c>
@@ -6655,7 +6691,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>378</v>
       </c>
@@ -6669,7 +6705,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>380</v>
       </c>
@@ -6683,7 +6719,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>382</v>
       </c>
@@ -6697,7 +6733,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>384</v>
       </c>
@@ -6711,7 +6747,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>386</v>
       </c>
@@ -6725,7 +6761,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>388</v>
       </c>
@@ -6739,7 +6775,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>390</v>
       </c>
@@ -6753,7 +6789,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>392</v>
       </c>
@@ -6767,7 +6803,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>394</v>
       </c>
@@ -6781,7 +6817,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>396</v>
       </c>
@@ -6795,7 +6831,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>398</v>
       </c>
@@ -6809,7 +6845,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>400</v>
       </c>
@@ -6823,7 +6859,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>402</v>
       </c>
@@ -6837,7 +6873,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1405</v>
       </c>
@@ -6851,7 +6887,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>1407</v>
       </c>
@@ -6865,7 +6901,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>404</v>
       </c>
@@ -6879,7 +6915,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>406</v>
       </c>
@@ -6893,7 +6929,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>408</v>
       </c>
@@ -6907,7 +6943,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>410</v>
       </c>
@@ -6921,7 +6957,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>412</v>
       </c>
@@ -6935,7 +6971,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>414</v>
       </c>
@@ -6949,7 +6985,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>416</v>
       </c>
@@ -6963,7 +6999,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>418</v>
       </c>
@@ -6977,7 +7013,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>420</v>
       </c>
@@ -6991,7 +7027,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>422</v>
       </c>
@@ -7005,7 +7041,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>424</v>
       </c>
@@ -7019,7 +7055,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>426</v>
       </c>
@@ -7033,7 +7069,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>428</v>
       </c>
@@ -7047,7 +7083,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>430</v>
       </c>
@@ -7061,7 +7097,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>432</v>
       </c>
@@ -7075,7 +7111,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>434</v>
       </c>
@@ -7089,7 +7125,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>436</v>
       </c>
@@ -7103,7 +7139,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>438</v>
       </c>
@@ -7117,7 +7153,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>440</v>
       </c>
@@ -7131,7 +7167,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>442</v>
       </c>
@@ -7145,7 +7181,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>444</v>
       </c>
@@ -7159,7 +7195,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>446</v>
       </c>
@@ -7173,7 +7209,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>448</v>
       </c>
@@ -7187,7 +7223,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>450</v>
       </c>
@@ -7201,7 +7237,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>452</v>
       </c>
@@ -7215,7 +7251,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>454</v>
       </c>
@@ -7229,7 +7265,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>456</v>
       </c>
@@ -7243,7 +7279,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>458</v>
       </c>
@@ -7257,7 +7293,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>460</v>
       </c>
@@ -7271,7 +7307,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>462</v>
       </c>
@@ -7285,7 +7321,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>464</v>
       </c>
@@ -7299,7 +7335,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>466</v>
       </c>
@@ -7313,7 +7349,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>468</v>
       </c>
@@ -7327,7 +7363,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>470</v>
       </c>
@@ -7341,7 +7377,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>472</v>
       </c>
@@ -7355,7 +7391,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>474</v>
       </c>
@@ -7369,7 +7405,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>476</v>
       </c>
@@ -7383,7 +7419,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>478</v>
       </c>
@@ -7397,7 +7433,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>480</v>
       </c>
@@ -7411,7 +7447,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>482</v>
       </c>
@@ -7425,7 +7461,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>484</v>
       </c>
@@ -7439,7 +7475,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>1409</v>
       </c>
@@ -7453,7 +7489,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>486</v>
       </c>
@@ -7467,7 +7503,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>488</v>
       </c>
@@ -7481,7 +7517,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>490</v>
       </c>
@@ -7495,7 +7531,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>492</v>
       </c>
@@ -7509,7 +7545,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>494</v>
       </c>
@@ -7523,7 +7559,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>496</v>
       </c>
@@ -7537,7 +7573,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>498</v>
       </c>
@@ -7551,7 +7587,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>500</v>
       </c>
@@ -7565,7 +7601,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>502</v>
       </c>
@@ -7579,7 +7615,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>504</v>
       </c>
@@ -7593,7 +7629,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>506</v>
       </c>
@@ -7607,7 +7643,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>507</v>
       </c>
@@ -7621,7 +7657,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>508</v>
       </c>
@@ -7635,7 +7671,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>509</v>
       </c>
@@ -7649,7 +7685,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>510</v>
       </c>
@@ -7663,7 +7699,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>512</v>
       </c>
@@ -7677,7 +7713,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>514</v>
       </c>
@@ -7691,7 +7727,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>516</v>
       </c>
@@ -7705,7 +7741,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>518</v>
       </c>
@@ -7719,7 +7755,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>520</v>
       </c>
@@ -7733,7 +7769,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>522</v>
       </c>
@@ -7747,7 +7783,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>524</v>
       </c>
@@ -7761,7 +7797,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>525</v>
       </c>
@@ -7775,7 +7811,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>527</v>
       </c>
@@ -7789,7 +7825,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>529</v>
       </c>
@@ -7803,7 +7839,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>531</v>
       </c>
@@ -7817,7 +7853,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>533</v>
       </c>
@@ -7831,7 +7867,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>535</v>
       </c>
@@ -7845,7 +7881,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>537</v>
       </c>
@@ -7859,7 +7895,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>539</v>
       </c>
@@ -7873,7 +7909,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>541</v>
       </c>
@@ -7887,7 +7923,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>543</v>
       </c>
@@ -7901,7 +7937,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>545</v>
       </c>
@@ -7915,7 +7951,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>547</v>
       </c>
@@ -7929,7 +7965,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>549</v>
       </c>
@@ -7943,7 +7979,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>551</v>
       </c>
@@ -7957,7 +7993,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>553</v>
       </c>
@@ -7971,7 +8007,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>555</v>
       </c>
@@ -7985,7 +8021,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>557</v>
       </c>
@@ -7999,7 +8035,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>559</v>
       </c>
@@ -8013,7 +8049,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>561</v>
       </c>
@@ -8027,7 +8063,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>563</v>
       </c>
@@ -8041,7 +8077,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>565</v>
       </c>
@@ -8055,7 +8091,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>567</v>
       </c>
@@ -8069,7 +8105,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>569</v>
       </c>
@@ -8083,7 +8119,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>571</v>
       </c>
@@ -8097,7 +8133,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>573</v>
       </c>
@@ -8111,7 +8147,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>575</v>
       </c>
@@ -8125,7 +8161,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>577</v>
       </c>
@@ -8139,7 +8175,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>579</v>
       </c>
@@ -8153,7 +8189,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>581</v>
       </c>
@@ -8167,7 +8203,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>583</v>
       </c>
@@ -8181,7 +8217,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>585</v>
       </c>
@@ -8195,7 +8231,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>587</v>
       </c>
@@ -8209,7 +8245,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>589</v>
       </c>
@@ -8223,7 +8259,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>591</v>
       </c>
@@ -8237,7 +8273,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>593</v>
       </c>
@@ -8251,7 +8287,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>595</v>
       </c>
@@ -8265,7 +8301,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>597</v>
       </c>
@@ -8279,7 +8315,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>599</v>
       </c>
@@ -8293,7 +8329,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>601</v>
       </c>
@@ -8307,7 +8343,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>603</v>
       </c>
@@ -8321,7 +8357,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>605</v>
       </c>
@@ -8335,7 +8371,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>607</v>
       </c>
@@ -8349,7 +8385,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>609</v>
       </c>
@@ -8363,7 +8399,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>611</v>
       </c>
@@ -8377,7 +8413,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>613</v>
       </c>
@@ -8391,7 +8427,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>615</v>
       </c>
@@ -8405,7 +8441,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>617</v>
       </c>
@@ -8419,7 +8455,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>619</v>
       </c>
@@ -8433,7 +8469,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>621</v>
       </c>
@@ -8447,7 +8483,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>623</v>
       </c>
@@ -8461,7 +8497,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>625</v>
       </c>
@@ -8475,7 +8511,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>627</v>
       </c>
@@ -8489,7 +8525,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>629</v>
       </c>
@@ -8503,7 +8539,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>631</v>
       </c>
@@ -8517,7 +8553,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>633</v>
       </c>
@@ -8531,7 +8567,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>635</v>
       </c>
@@ -8545,7 +8581,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>637</v>
       </c>
@@ -8559,7 +8595,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>639</v>
       </c>
@@ -8573,7 +8609,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>641</v>
       </c>
@@ -8587,7 +8623,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>642</v>
       </c>
@@ -8601,7 +8637,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>644</v>
       </c>
@@ -8615,7 +8651,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>646</v>
       </c>
@@ -8629,7 +8665,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>648</v>
       </c>
@@ -8643,7 +8679,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>650</v>
       </c>
@@ -8657,7 +8693,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>652</v>
       </c>
@@ -8671,7 +8707,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>654</v>
       </c>
@@ -8685,7 +8721,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>656</v>
       </c>
@@ -8699,7 +8735,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>658</v>
       </c>
@@ -8713,7 +8749,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>660</v>
       </c>
@@ -8727,7 +8763,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>662</v>
       </c>
@@ -8741,7 +8777,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>664</v>
       </c>
@@ -8755,7 +8791,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>666</v>
       </c>
@@ -8769,7 +8805,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>668</v>
       </c>
@@ -8783,7 +8819,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>670</v>
       </c>
@@ -8797,7 +8833,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>672</v>
       </c>
@@ -8811,7 +8847,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>674</v>
       </c>
@@ -8825,7 +8861,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>676</v>
       </c>
@@ -8839,7 +8875,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>678</v>
       </c>
@@ -8853,7 +8889,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>680</v>
       </c>
@@ -8867,7 +8903,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>682</v>
       </c>
@@ -8881,7 +8917,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>684</v>
       </c>
@@ -8895,7 +8931,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>686</v>
       </c>
@@ -8909,7 +8945,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>688</v>
       </c>
@@ -8923,7 +8959,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1412</v>
       </c>
@@ -8937,7 +8973,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1414</v>
       </c>
@@ -8951,7 +8987,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1416</v>
       </c>
@@ -8965,7 +9001,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1418</v>
       </c>
@@ -8979,7 +9015,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1420</v>
       </c>
@@ -8993,7 +9029,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1422</v>
       </c>
@@ -9007,7 +9043,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1424</v>
       </c>
@@ -9021,7 +9057,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>690</v>
       </c>
@@ -9035,7 +9071,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>692</v>
       </c>
@@ -9049,7 +9085,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>694</v>
       </c>
@@ -9063,7 +9099,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>696</v>
       </c>
@@ -9077,7 +9113,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>698</v>
       </c>
@@ -9091,7 +9127,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>700</v>
       </c>
@@ -9105,7 +9141,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>702</v>
       </c>
@@ -9119,7 +9155,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>704</v>
       </c>
@@ -9133,7 +9169,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>706</v>
       </c>
@@ -9147,7 +9183,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>708</v>
       </c>
@@ -9161,7 +9197,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>710</v>
       </c>
@@ -9175,7 +9211,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>712</v>
       </c>
@@ -9189,7 +9225,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>714</v>
       </c>
@@ -9203,7 +9239,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>716</v>
       </c>
@@ -9217,7 +9253,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>718</v>
       </c>
@@ -9231,7 +9267,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>720</v>
       </c>
@@ -9245,7 +9281,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>722</v>
       </c>
@@ -9259,7 +9295,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>724</v>
       </c>
@@ -9273,7 +9309,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>726</v>
       </c>
@@ -9287,7 +9323,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>728</v>
       </c>
@@ -9301,7 +9337,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>730</v>
       </c>
@@ -9315,7 +9351,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>732</v>
       </c>
@@ -9329,7 +9365,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>734</v>
       </c>
@@ -9343,7 +9379,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>736</v>
       </c>
@@ -9357,7 +9393,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>738</v>
       </c>
@@ -9371,7 +9407,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>740</v>
       </c>
@@ -9385,7 +9421,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>742</v>
       </c>
@@ -9399,7 +9435,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>744</v>
       </c>
@@ -9413,7 +9449,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>746</v>
       </c>
@@ -9427,7 +9463,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>748</v>
       </c>
@@ -9441,7 +9477,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>750</v>
       </c>
@@ -9455,7 +9491,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>752</v>
       </c>
@@ -9469,7 +9505,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>754</v>
       </c>
@@ -9483,7 +9519,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>756</v>
       </c>
@@ -9497,7 +9533,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>758</v>
       </c>
@@ -9511,7 +9547,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>760</v>
       </c>
@@ -9525,7 +9561,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>762</v>
       </c>
@@ -9539,7 +9575,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>764</v>
       </c>
@@ -9553,7 +9589,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>766</v>
       </c>
@@ -9567,7 +9603,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>768</v>
       </c>
@@ -9581,7 +9617,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>770</v>
       </c>
@@ -9595,7 +9631,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>772</v>
       </c>
@@ -9609,7 +9645,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>774</v>
       </c>
@@ -9623,7 +9659,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>776</v>
       </c>
@@ -9637,7 +9673,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>778</v>
       </c>
@@ -9651,7 +9687,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>780</v>
       </c>
@@ -9665,7 +9701,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>782</v>
       </c>
@@ -9679,7 +9715,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>784</v>
       </c>
@@ -9693,7 +9729,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>786</v>
       </c>
@@ -9707,7 +9743,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>788</v>
       </c>
@@ -9721,7 +9757,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>790</v>
       </c>
@@ -9735,7 +9771,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>792</v>
       </c>
@@ -9749,7 +9785,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>794</v>
       </c>
@@ -9763,7 +9799,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>796</v>
       </c>
@@ -9777,7 +9813,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>798</v>
       </c>
@@ -9791,7 +9827,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>800</v>
       </c>
@@ -9805,7 +9841,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>802</v>
       </c>
@@ -9819,7 +9855,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>804</v>
       </c>
@@ -9833,7 +9869,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>806</v>
       </c>
@@ -9847,7 +9883,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>808</v>
       </c>
@@ -9861,7 +9897,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>810</v>
       </c>
@@ -9875,7 +9911,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>812</v>
       </c>
@@ -9889,7 +9925,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>814</v>
       </c>
@@ -9903,7 +9939,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>816</v>
       </c>
@@ -9917,7 +9953,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>818</v>
       </c>
@@ -9931,7 +9967,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>820</v>
       </c>
@@ -9945,7 +9981,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>822</v>
       </c>
@@ -9959,7 +9995,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>824</v>
       </c>
@@ -9973,7 +10009,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>826</v>
       </c>
@@ -9987,7 +10023,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>828</v>
       </c>
@@ -10001,7 +10037,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>830</v>
       </c>
@@ -10015,7 +10051,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>832</v>
       </c>
@@ -10029,7 +10065,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>834</v>
       </c>
@@ -10043,7 +10079,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>836</v>
       </c>
@@ -10057,7 +10093,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>838</v>
       </c>
@@ -10071,7 +10107,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1426</v>
       </c>
@@ -10085,7 +10121,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1428</v>
       </c>
@@ -10099,7 +10135,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1430</v>
       </c>
@@ -10113,7 +10149,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1432</v>
       </c>
@@ -10127,7 +10163,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1434</v>
       </c>
@@ -10141,7 +10177,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>840</v>
       </c>
@@ -10155,7 +10191,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>842</v>
       </c>
@@ -10169,7 +10205,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>844</v>
       </c>
@@ -10183,7 +10219,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>846</v>
       </c>
@@ -10197,7 +10233,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>848</v>
       </c>
@@ -10211,7 +10247,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>850</v>
       </c>
@@ -10225,7 +10261,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>852</v>
       </c>
@@ -10239,7 +10275,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>854</v>
       </c>
@@ -10253,7 +10289,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>856</v>
       </c>
@@ -10267,7 +10303,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>858</v>
       </c>
@@ -10281,7 +10317,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>860</v>
       </c>
@@ -10295,7 +10331,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>862</v>
       </c>
@@ -10309,7 +10345,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>864</v>
       </c>
@@ -10323,7 +10359,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>866</v>
       </c>
@@ -10337,7 +10373,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>868</v>
       </c>
@@ -10351,7 +10387,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>870</v>
       </c>
@@ -10365,7 +10401,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>872</v>
       </c>
@@ -10379,7 +10415,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>874</v>
       </c>
@@ -10393,7 +10429,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>876</v>
       </c>
@@ -10407,7 +10443,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>878</v>
       </c>
@@ -10421,7 +10457,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>880</v>
       </c>
@@ -10435,7 +10471,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>882</v>
       </c>
@@ -10449,7 +10485,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>884</v>
       </c>
@@ -10463,7 +10499,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>886</v>
       </c>
@@ -10477,7 +10513,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>888</v>
       </c>
@@ -10491,7 +10527,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>890</v>
       </c>
@@ -10505,7 +10541,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>892</v>
       </c>
@@ -10519,7 +10555,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>894</v>
       </c>
@@ -10533,7 +10569,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>896</v>
       </c>
@@ -10547,7 +10583,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>898</v>
       </c>
@@ -10561,7 +10597,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>900</v>
       </c>
@@ -10575,7 +10611,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>902</v>
       </c>
@@ -10589,7 +10625,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>904</v>
       </c>
@@ -10603,7 +10639,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>906</v>
       </c>
@@ -10617,7 +10653,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>908</v>
       </c>
@@ -10631,7 +10667,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>910</v>
       </c>
@@ -10645,7 +10681,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>912</v>
       </c>
@@ -10659,7 +10695,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>914</v>
       </c>
@@ -10673,7 +10709,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>916</v>
       </c>
@@ -10687,7 +10723,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>918</v>
       </c>
@@ -10701,7 +10737,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>920</v>
       </c>
@@ -10715,7 +10751,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>922</v>
       </c>
@@ -10729,7 +10765,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>924</v>
       </c>
@@ -10743,7 +10779,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>926</v>
       </c>
@@ -10757,7 +10793,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>928</v>
       </c>
@@ -10771,7 +10807,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>930</v>
       </c>
@@ -10785,7 +10821,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>931</v>
       </c>
@@ -10799,7 +10835,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>933</v>
       </c>
@@ -10813,7 +10849,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>935</v>
       </c>
@@ -10827,7 +10863,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>937</v>
       </c>
@@ -10841,7 +10877,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>939</v>
       </c>
@@ -10855,7 +10891,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>941</v>
       </c>
@@ -10869,7 +10905,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>943</v>
       </c>
@@ -10883,7 +10919,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>945</v>
       </c>
@@ -10897,7 +10933,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>947</v>
       </c>
@@ -10911,7 +10947,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>949</v>
       </c>
@@ -10925,7 +10961,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>951</v>
       </c>
@@ -10939,7 +10975,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>953</v>
       </c>
@@ -10953,7 +10989,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>955</v>
       </c>
@@ -10967,7 +11003,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>957</v>
       </c>
@@ -10981,7 +11017,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>959</v>
       </c>
@@ -10995,7 +11031,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1437</v>
       </c>
@@ -11009,7 +11045,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1439</v>
       </c>
@@ -11023,7 +11059,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1441</v>
       </c>
@@ -11037,7 +11073,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1443</v>
       </c>
@@ -11051,7 +11087,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1445</v>
       </c>
@@ -11065,7 +11101,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>961</v>
       </c>
@@ -11079,7 +11115,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>963</v>
       </c>
@@ -11093,7 +11129,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>965</v>
       </c>
@@ -11107,7 +11143,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>967</v>
       </c>
@@ -11121,7 +11157,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>969</v>
       </c>
@@ -11135,7 +11171,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>971</v>
       </c>
@@ -11149,7 +11185,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>973</v>
       </c>
@@ -11163,7 +11199,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>975</v>
       </c>
@@ -11177,7 +11213,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>977</v>
       </c>
@@ -11191,7 +11227,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>979</v>
       </c>
@@ -11205,7 +11241,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>981</v>
       </c>
@@ -11219,7 +11255,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>983</v>
       </c>
@@ -11233,7 +11269,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>985</v>
       </c>
@@ -11247,7 +11283,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>987</v>
       </c>
@@ -11261,7 +11297,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>989</v>
       </c>
@@ -11275,7 +11311,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>992</v>
       </c>
@@ -11289,7 +11325,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>994</v>
       </c>
@@ -11303,7 +11339,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>996</v>
       </c>
@@ -11317,7 +11353,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>998</v>
       </c>
@@ -11331,7 +11367,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1000</v>
       </c>
@@ -11345,7 +11381,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1002</v>
       </c>
@@ -11359,7 +11395,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1004</v>
       </c>
@@ -11373,7 +11409,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1006</v>
       </c>
@@ -11387,7 +11423,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1008</v>
       </c>
@@ -11401,7 +11437,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1010</v>
       </c>
@@ -11415,7 +11451,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1012</v>
       </c>
@@ -11429,7 +11465,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1014</v>
       </c>
@@ -11443,7 +11479,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1016</v>
       </c>
@@ -11457,7 +11493,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1018</v>
       </c>
@@ -11471,7 +11507,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1020</v>
       </c>
@@ -11485,7 +11521,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1022</v>
       </c>
@@ -11499,7 +11535,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1024</v>
       </c>
@@ -11513,7 +11549,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1026</v>
       </c>
@@ -11527,7 +11563,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1028</v>
       </c>
@@ -11541,7 +11577,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1030</v>
       </c>
@@ -11555,7 +11591,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1032</v>
       </c>
@@ -11569,7 +11605,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1034</v>
       </c>
@@ -11583,7 +11619,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1036</v>
       </c>
@@ -11597,7 +11633,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1038</v>
       </c>
@@ -11611,7 +11647,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1040</v>
       </c>
@@ -11625,7 +11661,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1042</v>
       </c>
@@ -11639,7 +11675,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1044</v>
       </c>
@@ -11653,7 +11689,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1046</v>
       </c>
@@ -11667,7 +11703,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1048</v>
       </c>
@@ -11681,7 +11717,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1050</v>
       </c>
@@ -11695,7 +11731,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1052</v>
       </c>
@@ -11709,7 +11745,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1054</v>
       </c>
@@ -11723,7 +11759,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1056</v>
       </c>
@@ -11737,7 +11773,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1058</v>
       </c>
@@ -11751,7 +11787,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1060</v>
       </c>
@@ -11765,7 +11801,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1062</v>
       </c>
@@ -11779,7 +11815,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1064</v>
       </c>
@@ -11793,7 +11829,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1066</v>
       </c>
@@ -11807,7 +11843,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1447</v>
       </c>
@@ -11821,7 +11857,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1449</v>
       </c>
@@ -11835,7 +11871,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1451</v>
       </c>
@@ -11849,7 +11885,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1453</v>
       </c>
@@ -11863,7 +11899,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>1455</v>
       </c>
@@ -11877,7 +11913,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>1457</v>
       </c>
@@ -11891,7 +11927,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>1459</v>
       </c>
@@ -11905,7 +11941,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>1461</v>
       </c>
@@ -11919,7 +11955,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>1463</v>
       </c>
@@ -11933,7 +11969,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>1465</v>
       </c>
@@ -11947,7 +11983,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>1467</v>
       </c>
@@ -11961,7 +11997,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>1469</v>
       </c>
@@ -11975,7 +12011,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>1471</v>
       </c>
@@ -11989,7 +12025,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>1473</v>
       </c>
@@ -12003,7 +12039,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>1475</v>
       </c>
@@ -12017,7 +12053,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>1477</v>
       </c>
@@ -12031,7 +12067,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>1479</v>
       </c>
@@ -12045,7 +12081,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>1481</v>
       </c>
@@ -12059,7 +12095,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>1068</v>
       </c>
@@ -12073,7 +12109,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>1070</v>
       </c>
@@ -12087,7 +12123,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>1072</v>
       </c>
@@ -12101,7 +12137,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1074</v>
       </c>
@@ -12115,7 +12151,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>1076</v>
       </c>
@@ -12129,7 +12165,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>1078</v>
       </c>
@@ -12143,7 +12179,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>1079</v>
       </c>
@@ -12157,7 +12193,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1081</v>
       </c>
@@ -12171,7 +12207,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1083</v>
       </c>
@@ -12185,7 +12221,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>1085</v>
       </c>
@@ -12199,7 +12235,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1087</v>
       </c>
@@ -12213,7 +12249,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1089</v>
       </c>
@@ -12227,7 +12263,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1091</v>
       </c>
@@ -12241,7 +12277,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1093</v>
       </c>
@@ -12255,7 +12291,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1095</v>
       </c>
@@ -12269,7 +12305,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1097</v>
       </c>
@@ -12283,7 +12319,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1099</v>
       </c>
@@ -12297,7 +12333,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1101</v>
       </c>
@@ -12311,7 +12347,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1103</v>
       </c>
@@ -12325,7 +12361,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1105</v>
       </c>
@@ -12339,7 +12375,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>1107</v>
       </c>
@@ -12353,7 +12389,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1109</v>
       </c>
@@ -12367,7 +12403,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1111</v>
       </c>
@@ -12381,7 +12417,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>102</v>
       </c>
@@ -12395,7 +12431,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>8</v>
       </c>
@@ -12409,7 +12445,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>6</v>
       </c>
@@ -12423,7 +12459,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>83</v>
       </c>
@@ -12437,7 +12473,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>29</v>
       </c>
@@ -12451,7 +12487,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>33</v>
       </c>
@@ -12465,7 +12501,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>15</v>
       </c>
@@ -12479,7 +12515,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>109</v>
       </c>
@@ -12493,7 +12529,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>105</v>
       </c>
@@ -12507,7 +12543,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>79</v>
       </c>
@@ -12521,7 +12557,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>14</v>
       </c>
@@ -12535,7 +12571,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1114</v>
       </c>
@@ -12549,7 +12585,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1483</v>
       </c>
@@ -12563,7 +12599,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1485</v>
       </c>
@@ -12577,7 +12613,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>44</v>
       </c>
@@ -12591,7 +12627,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>45</v>
       </c>
@@ -12605,7 +12641,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>85</v>
       </c>
@@ -12619,7 +12655,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>46</v>
       </c>
@@ -12633,7 +12669,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>40</v>
       </c>
@@ -12647,7 +12683,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1490</v>
       </c>
@@ -12661,7 +12697,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>111</v>
       </c>
@@ -12675,7 +12711,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>19</v>
       </c>
@@ -12689,7 +12725,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>36</v>
       </c>
@@ -12703,7 +12739,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>1116</v>
       </c>
@@ -12717,7 +12753,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1120</v>
       </c>
@@ -12731,7 +12767,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1121</v>
       </c>
@@ -12745,7 +12781,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>136</v>
       </c>
@@ -12759,7 +12795,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1123</v>
       </c>
@@ -12773,7 +12809,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1124</v>
       </c>
@@ -12787,7 +12823,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1125</v>
       </c>
@@ -12801,7 +12837,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>12</v>
       </c>
@@ -12815,7 +12851,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1126</v>
       </c>
@@ -12829,7 +12865,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>81</v>
       </c>
@@ -12843,7 +12879,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1128</v>
       </c>
@@ -12857,7 +12893,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>96</v>
       </c>
@@ -12871,7 +12907,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>1130</v>
       </c>
@@ -12885,7 +12921,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>1132</v>
       </c>
@@ -12899,7 +12935,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>1134</v>
       </c>
@@ -12913,7 +12949,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>35</v>
       </c>
@@ -12927,7 +12963,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>1136</v>
       </c>
@@ -12941,7 +12977,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>1138</v>
       </c>
@@ -12955,7 +12991,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>1494</v>
       </c>
@@ -12969,7 +13005,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>1496</v>
       </c>
@@ -12983,7 +13019,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>1498</v>
       </c>
@@ -12997,7 +13033,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>1500</v>
       </c>
@@ -13011,7 +13047,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>48</v>
       </c>
@@ -13025,7 +13061,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>100</v>
       </c>
@@ -13039,7 +13075,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>86</v>
       </c>
@@ -13053,7 +13089,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>88</v>
       </c>
@@ -13067,7 +13103,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>42</v>
       </c>
@@ -13081,7 +13117,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>133</v>
       </c>
@@ -13095,7 +13131,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1139</v>
       </c>
@@ -13109,7 +13145,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>121</v>
       </c>
@@ -13123,7 +13159,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>91</v>
       </c>
@@ -13137,7 +13173,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>95</v>
       </c>
@@ -13151,7 +13187,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>93</v>
       </c>
@@ -13165,7 +13201,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>135</v>
       </c>
@@ -13179,7 +13215,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>65</v>
       </c>
@@ -13193,7 +13229,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1144</v>
       </c>
@@ -13207,7 +13243,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>117</v>
       </c>
@@ -13221,7 +13257,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>38</v>
       </c>
@@ -13235,7 +13271,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>131</v>
       </c>
@@ -13249,7 +13285,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>119</v>
       </c>
@@ -13263,7 +13299,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>90</v>
       </c>
@@ -13277,7 +13313,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1147</v>
       </c>
@@ -13291,7 +13327,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>94</v>
       </c>
@@ -13305,7 +13341,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1150</v>
       </c>
@@ -13319,7 +13355,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1152</v>
       </c>
@@ -13333,7 +13369,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1154</v>
       </c>
@@ -13347,7 +13383,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>1156</v>
       </c>
@@ -13361,7 +13397,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>1158</v>
       </c>
@@ -13375,7 +13411,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>50</v>
       </c>
@@ -13389,7 +13425,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>10</v>
       </c>
@@ -13403,7 +13439,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>69</v>
       </c>
@@ -13417,7 +13453,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>3</v>
       </c>
@@ -13431,7 +13467,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>113</v>
       </c>
@@ -13445,7 +13481,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>71</v>
       </c>
@@ -13459,7 +13495,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>98</v>
       </c>
@@ -13473,7 +13509,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>107</v>
       </c>
@@ -13487,7 +13523,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>1160</v>
       </c>
@@ -13501,7 +13537,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>125</v>
       </c>
@@ -13515,7 +13551,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>17</v>
       </c>
@@ -13529,7 +13565,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>1162</v>
       </c>
@@ -13543,7 +13579,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>1164</v>
       </c>
@@ -13557,7 +13593,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>1166</v>
       </c>
@@ -13571,7 +13607,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>1168</v>
       </c>
@@ -13585,7 +13621,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>1170</v>
       </c>
@@ -13599,7 +13635,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>1172</v>
       </c>
@@ -13613,7 +13649,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>1174</v>
       </c>
@@ -13627,7 +13663,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>52</v>
       </c>
@@ -13641,7 +13677,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>1176</v>
       </c>
@@ -13655,7 +13691,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>1178</v>
       </c>
@@ -13669,7 +13705,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>1180</v>
       </c>
@@ -13683,7 +13719,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>54</v>
       </c>
@@ -13697,7 +13733,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>56</v>
       </c>
@@ -13711,7 +13747,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>1182</v>
       </c>
@@ -13725,7 +13761,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>58</v>
       </c>
@@ -13739,7 +13775,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>1184</v>
       </c>
@@ -13753,7 +13789,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>1186</v>
       </c>
@@ -13767,7 +13803,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>61</v>
       </c>
@@ -13781,7 +13817,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>1188</v>
       </c>
@@ -13795,7 +13831,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>63</v>
       </c>
@@ -13809,7 +13845,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>1190</v>
       </c>
@@ -13823,7 +13859,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>1192</v>
       </c>
@@ -13837,7 +13873,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>1194</v>
       </c>
@@ -13851,7 +13887,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>1196</v>
       </c>
@@ -13865,7 +13901,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>1198</v>
       </c>
@@ -13879,7 +13915,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>1200</v>
       </c>
@@ -13893,7 +13929,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>1202</v>
       </c>
@@ -13907,7 +13943,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>73</v>
       </c>
@@ -13921,7 +13957,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>75</v>
       </c>
@@ -13935,7 +13971,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>1204</v>
       </c>
@@ -13949,7 +13985,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>1206</v>
       </c>
@@ -13963,7 +13999,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>1208</v>
       </c>
@@ -13977,7 +14013,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>31</v>
       </c>
@@ -13991,7 +14027,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>115</v>
       </c>
@@ -14005,7 +14041,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>138</v>
       </c>
@@ -14019,7 +14055,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>1210</v>
       </c>
@@ -14033,7 +14069,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>21</v>
       </c>
@@ -14047,7 +14083,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>67</v>
       </c>
@@ -14061,7 +14097,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>1212</v>
       </c>
@@ -14075,7 +14111,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>1214</v>
       </c>
@@ -14089,7 +14125,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>123</v>
       </c>
@@ -14103,7 +14139,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>1216</v>
       </c>
@@ -14117,7 +14153,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>127</v>
       </c>
@@ -14131,7 +14167,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>1217</v>
       </c>
@@ -14145,7 +14181,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>1219</v>
       </c>
@@ -14159,7 +14195,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>1221</v>
       </c>
@@ -14173,7 +14209,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>1223</v>
       </c>
@@ -14187,7 +14223,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>1225</v>
       </c>
@@ -14201,7 +14237,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>23</v>
       </c>
@@ -14215,7 +14251,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>1227</v>
       </c>
@@ -14229,7 +14265,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>1229</v>
       </c>
@@ -14243,7 +14279,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>25</v>
       </c>
@@ -14257,7 +14293,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>1231</v>
       </c>
@@ -14271,7 +14307,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>27</v>
       </c>
@@ -14285,7 +14321,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>1233</v>
       </c>
@@ -14299,7 +14335,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>1235</v>
       </c>
@@ -14313,7 +14349,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>1237</v>
       </c>
@@ -14327,7 +14363,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>1239</v>
       </c>
@@ -14341,7 +14377,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>1241</v>
       </c>
@@ -14355,7 +14391,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>1243</v>
       </c>
@@ -14369,7 +14405,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>1245</v>
       </c>
@@ -14383,7 +14419,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>1247</v>
       </c>
@@ -14397,7 +14433,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>1249</v>
       </c>
@@ -14411,7 +14447,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>1251</v>
       </c>
@@ -14425,7 +14461,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>1253</v>
       </c>
@@ -14439,7 +14475,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>1255</v>
       </c>
@@ -14453,7 +14489,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>1257</v>
       </c>
@@ -14467,7 +14503,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>1259</v>
       </c>
@@ -14481,7 +14517,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>1261</v>
       </c>
@@ -14495,7 +14531,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>1263</v>
       </c>
@@ -14509,7 +14545,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>1265</v>
       </c>
@@ -14523,7 +14559,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>1267</v>
       </c>
@@ -14537,7 +14573,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>1269</v>
       </c>
@@ -14551,7 +14587,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>1271</v>
       </c>
@@ -14565,7 +14601,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>1273</v>
       </c>
@@ -14579,7 +14615,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>1275</v>
       </c>
@@ -14593,7 +14629,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>1277</v>
       </c>
@@ -14607,7 +14643,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>1279</v>
       </c>
@@ -14621,7 +14657,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>1281</v>
       </c>
@@ -14635,7 +14671,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>1283</v>
       </c>
@@ -14649,7 +14685,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>1285</v>
       </c>
@@ -14663,7 +14699,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>1287</v>
       </c>
@@ -14677,7 +14713,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>1289</v>
       </c>
@@ -14691,7 +14727,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>1291</v>
       </c>
@@ -14705,7 +14741,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>1293</v>
       </c>
@@ -14719,7 +14755,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>1295</v>
       </c>
@@ -14733,7 +14769,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>1297</v>
       </c>
@@ -14747,7 +14783,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>1299</v>
       </c>
@@ -14761,7 +14797,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>1301</v>
       </c>
@@ -14775,7 +14811,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>1303</v>
       </c>
@@ -14789,7 +14825,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>1305</v>
       </c>
@@ -14803,7 +14839,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>1307</v>
       </c>
@@ -14817,7 +14853,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>1309</v>
       </c>
@@ -14831,7 +14867,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>1311</v>
       </c>
@@ -14845,7 +14881,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>1313</v>
       </c>
@@ -14859,7 +14895,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>1315</v>
       </c>
@@ -14873,7 +14909,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>1317</v>
       </c>
@@ -14887,7 +14923,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>1319</v>
       </c>
@@ -14901,7 +14937,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>1321</v>
       </c>
@@ -14915,7 +14951,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>1323</v>
       </c>
@@ -14929,7 +14965,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>1325</v>
       </c>
@@ -14943,7 +14979,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>1327</v>
       </c>
@@ -14957,7 +14993,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>1328</v>
       </c>
@@ -14971,7 +15007,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>1329</v>
       </c>
@@ -14985,7 +15021,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>1330</v>
       </c>
@@ -14999,7 +15035,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>1332</v>
       </c>
@@ -15013,7 +15049,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>1334</v>
       </c>
@@ -15027,7 +15063,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>1336</v>
       </c>
@@ -15041,7 +15077,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>1338</v>
       </c>
@@ -15055,7 +15091,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>1340</v>
       </c>
@@ -15069,7 +15105,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>1342</v>
       </c>
@@ -15083,7 +15119,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>1343</v>
       </c>
@@ -15097,7 +15133,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>1344</v>
       </c>
@@ -15111,7 +15147,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>1346</v>
       </c>
@@ -15125,7 +15161,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>1347</v>
       </c>
@@ -15139,7 +15175,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>1349</v>
       </c>
@@ -15153,7 +15189,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>1350</v>
       </c>
@@ -15167,7 +15203,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>1352</v>
       </c>
@@ -15181,7 +15217,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>1354</v>
       </c>
@@ -15195,7 +15231,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>1356</v>
       </c>
@@ -15209,7 +15245,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>1358</v>
       </c>
@@ -15223,7 +15259,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>1360</v>
       </c>
@@ -15237,7 +15273,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>1362</v>
       </c>
@@ -15251,7 +15287,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>1363</v>
       </c>
@@ -15265,7 +15301,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>1364</v>
       </c>
@@ -15279,7 +15315,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>1365</v>
       </c>
@@ -15293,7 +15329,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>1367</v>
       </c>
@@ -15307,7 +15343,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>1369</v>
       </c>
@@ -15321,7 +15357,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>1371</v>
       </c>
@@ -15335,7 +15371,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>1373</v>
       </c>
@@ -15349,7 +15385,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>1375</v>
       </c>
@@ -15363,7 +15399,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>1377</v>
       </c>
@@ -15377,7 +15413,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>1379</v>
       </c>
@@ -15391,7 +15427,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>1380</v>
       </c>
@@ -15405,7 +15441,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>1382</v>
       </c>
@@ -15419,7 +15455,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>1384</v>
       </c>
@@ -15433,7 +15469,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>1503</v>
       </c>
@@ -15445,6 +15481,104 @@
       </c>
       <c r="D749" t="s">
         <v>1511</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B750" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C750" t="s">
+        <v>5</v>
+      </c>
+      <c r="D750" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B751" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C751" t="s">
+        <v>142</v>
+      </c>
+      <c r="D751" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B752" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C752" t="s">
+        <v>142</v>
+      </c>
+      <c r="D752" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B753" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C753" t="s">
+        <v>142</v>
+      </c>
+      <c r="D753" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B754" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C754" t="s">
+        <v>142</v>
+      </c>
+      <c r="D754" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A755" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B755" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C755" t="s">
+        <v>142</v>
+      </c>
+      <c r="D755" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B756" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C756" t="s">
+        <v>142</v>
+      </c>
+      <c r="D756" t="s">
+        <v>1508</v>
       </c>
     </row>
   </sheetData>
